--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134960434</v>
+        <v>135253562</v>
       </c>
       <c r="B2" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448461</v>
+        <v>448572</v>
       </c>
       <c r="R2" t="n">
-        <v>6754155</v>
+        <v>6754105</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +793,470 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134960434</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>448461</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6754155</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135254122</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>448530</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135254424</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448455</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135254634</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135253562</v>
+        <v>135254909</v>
       </c>
       <c r="B2" t="n">
-        <v>99195</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448572</v>
+        <v>448449</v>
       </c>
       <c r="R2" t="n">
-        <v>6754105</v>
+        <v>6754213</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,42 +792,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134960434</v>
+        <v>135253562</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448461</v>
+        <v>448572</v>
       </c>
       <c r="R3" t="n">
-        <v>6754155</v>
+        <v>6754105</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135254122</v>
+        <v>134960434</v>
       </c>
       <c r="B4" t="n">
         <v>79131</v>
@@ -942,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448530</v>
+        <v>448461</v>
       </c>
       <c r="R4" t="n">
-        <v>6754137</v>
+        <v>6754155</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,22 +987,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135254424</v>
+        <v>135254122</v>
       </c>
       <c r="B5" t="n">
         <v>79131</v>
@@ -1068,11 +1069,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Finnarmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448455</v>
+        <v>448530</v>
       </c>
       <c r="R5" t="n">
         <v>6754137</v>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1145,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135254634</v>
+        <v>135254424</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1174,7 +1175,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448449</v>
+        <v>448455</v>
       </c>
       <c r="R6" t="n">
-        <v>6754213</v>
+        <v>6754137</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1258,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135254634</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135254909</v>
+        <v>135463405</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448449</v>
+        <v>448467</v>
       </c>
       <c r="R2" t="n">
-        <v>6754213</v>
+        <v>6754103</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,62 +787,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135253562</v>
+        <v>135254909</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448572</v>
+        <v>448449</v>
       </c>
       <c r="R3" t="n">
-        <v>6754105</v>
+        <v>6754213</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,42 +904,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134960434</v>
+        <v>135253562</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448461</v>
+        <v>448572</v>
       </c>
       <c r="R4" t="n">
-        <v>6754155</v>
+        <v>6754105</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +983,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135254122</v>
+        <v>134960434</v>
       </c>
       <c r="B5" t="n">
         <v>79131</v>
@@ -1059,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1073,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448530</v>
+        <v>448461</v>
       </c>
       <c r="R5" t="n">
-        <v>6754137</v>
+        <v>6754155</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1103,22 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135254424</v>
+        <v>135254122</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1185,11 +1181,11 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Finnarmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448455</v>
+        <v>448530</v>
       </c>
       <c r="R6" t="n">
         <v>6754137</v>
@@ -1224,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135254634</v>
+        <v>135254424</v>
       </c>
       <c r="B7" t="n">
         <v>79131</v>
@@ -1291,7 +1287,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1305,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448449</v>
+        <v>448455</v>
       </c>
       <c r="R7" t="n">
-        <v>6754213</v>
+        <v>6754137</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1340,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,6 +1370,122 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135254634</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1254,6 +1279,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254122</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254424</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,8 +1521,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135463405</v>
       </c>
       <c r="B2" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135254909</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135253562</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>134960434</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>135254122</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>135254424</v>
       </c>
       <c r="B7" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>135254634</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135463405</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>135253562</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>135254122</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>135254424</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>135254634</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134960434</v>
+        <v>135463405</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448461</v>
+        <v>448467</v>
       </c>
       <c r="R2" t="n">
-        <v>6754155</v>
+        <v>6754103</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,13 +791,751 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135463405</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135254909</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254909</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135253562</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>448572</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6754105</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253562</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134960434</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448461</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6754155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134960434</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135254122</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448530</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254122</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135254424</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448455</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254424</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135254634</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254634</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>135253562</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135463405</v>
+        <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>93361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Venjan, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448467</v>
+        <v>448493</v>
       </c>
       <c r="R2" t="n">
-        <v>6754103</v>
+        <v>6754160</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,63 +786,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463405</t>
+          <t>https://artportalen.se/Sighting/135998276</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135254909</v>
+        <v>135998270</v>
       </c>
       <c r="B3" t="n">
-        <v>8461</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448449</v>
+        <v>448479</v>
       </c>
       <c r="R3" t="n">
-        <v>6754213</v>
+        <v>6754159</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254909</t>
+          <t>https://artportalen.se/Sighting/135998270</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135253562</v>
+        <v>135998273</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,51 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448572</v>
+        <v>448462</v>
       </c>
       <c r="R4" t="n">
-        <v>6754105</v>
+        <v>6754207</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,63 +1010,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135253562</t>
+          <t>https://artportalen.se/Sighting/135998273</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134960434</v>
+        <v>135998280</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448461</v>
+        <v>448505</v>
       </c>
       <c r="R5" t="n">
-        <v>6754155</v>
+        <v>6754233</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960434</t>
+          <t>https://artportalen.se/Sighting/135998280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135254122</v>
+        <v>135463405</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,46 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnarmyren, Dlr</t>
+          <t>Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448530</v>
+        <v>448467</v>
       </c>
       <c r="R6" t="n">
-        <v>6754137</v>
+        <v>6754103</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,22 +1193,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,16 +1239,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254122</t>
+          <t>https://artportalen.se/Sighting/135463405</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135254424</v>
+        <v>135998267</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,46 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448455</v>
+        <v>448474</v>
       </c>
       <c r="R7" t="n">
-        <v>6754137</v>
+        <v>6754109</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,22 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,16 +1351,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135254424</t>
+          <t>https://artportalen.se/Sighting/135998267</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135254634</v>
+        <v>135998268</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,46 +1368,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnarmyren, Finnarmyren, Dlr</t>
+          <t>Solbodarna 1, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448449</v>
+        <v>448454</v>
       </c>
       <c r="R8" t="n">
-        <v>6754213</v>
+        <v>6754130</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,22 +1422,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,7 +1463,1523 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135998268</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135998271</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448460</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6754193</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998271</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135998275</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448483</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6754192</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998275</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135998277</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448493</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6754160</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998277</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135998269</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448474</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6754148</v>
+      </c>
+      <c r="S12" t="n">
+        <v>61</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135998279</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>448518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6754202</v>
+      </c>
+      <c r="S13" t="n">
+        <v>19</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998279</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135254909</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254909</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135253562</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>448572</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6754105</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135253562</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134960434</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>448461</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6754155</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960434</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135254122</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>448530</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254122</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135254424</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>448455</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6754137</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135254424</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135254634</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Finnarmyren, Finnarmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>448449</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135254634</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135998274</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>448479</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6754192</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998274</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135998278</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Solbodarna 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>448514</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6754167</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135998278</t>
         </is>
       </c>
     </row>
@@ -1536,6 +2992,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93361</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135463405</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998270</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135998273</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135998280</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135998267</v>
       </c>
       <c r="B7" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135998268</v>
       </c>
       <c r="B8" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135998271</v>
       </c>
       <c r="B9" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135998275</v>
       </c>
       <c r="B10" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135998277</v>
       </c>
       <c r="B11" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>135998274</v>
       </c>
       <c r="B20" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>135998278</v>
       </c>
       <c r="B21" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998270</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135998273</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135998280</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135998267</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135998268</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135998271</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135998275</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135998277</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135998269</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135998279</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>135998274</v>
       </c>
       <c r="B20" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>135998278</v>
       </c>
       <c r="B21" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998270</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135998273</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135998280</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135998267</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135998268</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135998271</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135998275</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135998277</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135998269</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135998279</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>135998274</v>
       </c>
       <c r="B20" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>135998278</v>
       </c>
       <c r="B21" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28842-2026 artfynd.xlsx
+++ b/artfynd/A 28842-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135998276</v>
       </c>
       <c r="B2" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135998270</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135998273</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135998280</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135998267</v>
       </c>
       <c r="B7" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135998268</v>
       </c>
       <c r="B8" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135998271</v>
       </c>
       <c r="B9" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135998275</v>
       </c>
       <c r="B10" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135998277</v>
       </c>
       <c r="B11" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135998269</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135998279</v>
       </c>
       <c r="B13" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>135998274</v>
       </c>
       <c r="B20" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>135998278</v>
       </c>
       <c r="B21" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
